--- a/DateBase/orders/Nha Thu_2026-7-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-10.xlsx
@@ -602,6 +602,9 @@
         <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
 white_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -660,7 +663,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>025101510551010101010105551010950</v>
+        <v>0251015105510101010101055510109520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -606,9 +606,594 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>217_琉璃翠_Dynamic_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>4</v>
+      </c>
+      <c r="C27" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>5</v>
+      </c>
+      <c r="C33" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>514_松虫草紫_scabiosa purple_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>418_松虫草白_scabiosa white_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>6</v>
+      </c>
+      <c r="C39" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>603_康乃馨粉钻_darkpink_undefined_20stems</v>
+      </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F42" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>18_波浪黄洋桔梗_Wavy Yellow Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>7</v>
+      </c>
+      <c r="C44" t="str">
+        <v>470_海芋白_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>1</v>
+      </c>
+      <c r="C45" t="str">
+        <v>824_剑兰阿蒂娜_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>826_剑兰粉闪电_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>822_剑兰红丝绒_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>321_雪柳叶_Spiraea  leaves_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>316_尤加利叶大叶_Eucalyptus Cinerea_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>341_南天竹绿_undefined_Nandina domestica Thunb._1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>348_万年青_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>440_火棘果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>442_僵尸果（进口）_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>428_南蛇藤_Celastrus orbiculatus _undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2</v>
+      </c>
+      <c r="C57" t="str">
+        <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>788_国产直葱白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F61" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>550_蕾丝红色_lace flower brown_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F65" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>3</v>
+      </c>
+      <c r="C66" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F68" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F69" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="C70" t="str" xml:space="preserve">
+        <v xml:space="preserve">345_天竺少女_Cryptomeria
+Kashiwaba_undefined_1bunch</v>
+      </c>
+      <c r="F70" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F71" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F72" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F73" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="str">
+        <v>547_粉菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F74" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="str">
+        <v>430_长寿果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F75" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F76" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F77" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F78" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="str">
+        <v>832_康乃馨香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F79" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="str">
+        <v>608_康乃馨笑颜_undefined_undefined_20stems</v>
+      </c>
+      <c r="F80" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F81" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="str">
+        <v>600_康乃馨复古红_vintage red_undefined_20stems</v>
+      </c>
+      <c r="F82" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F83" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="str">
+        <v>890_康乃馨红绸_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F84" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F85" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F86" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="str">
+        <v>8_冰淇淋洋桔梗_Icecream Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F87" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F88" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="str">
+        <v>641_绿枫叶_maple leaf_undefined_1bunch</v>
+      </c>
+      <c r="F89" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F90" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -663,7 +1248,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0251015105510101010101055510109520</v>
+        <v>02510151055101010101010555101095201281091327111010132051010101014151015510555201510101053103152020101010555101010105151010551530551055151010155105100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-10.xlsx
@@ -1190,6 +1190,9 @@
       <c r="C91" t="str">
         <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
       </c>
+      <c r="F91" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1248,7 +1251,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02510151055101010101010555101095201281091327111010132051010101014151015510555201510101053103152020101010555101010105151010551530551055151010155105100</v>
+        <v>02510151055101010101010555101095201281091327111010132051010101014151015510555201510101053103152020101010555101010105151010551530551055151010155105101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1191,12 +1191,95 @@
         <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
       </c>
       <c r="F91" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>5</v>
+      </c>
+      <c r="C92" t="str">
+        <v>430_长寿果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F92" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F93" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F94" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="str">
+        <v>790_铁线莲粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F95" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F96" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>6</v>
+      </c>
+      <c r="C97" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F97" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+      <c r="F98" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" t="str">
+        <v>433_红豆_Hypericum red_undefined_1bunch</v>
+      </c>
+      <c r="F99" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" t="str">
+        <v>695_百合虎皮_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F100" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1251,7 +1334,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02510151055101010101010555101095201281091327111010132051010101014151015510555201510101053103152020101010555101010105151010551530551055151010155105101</v>
+        <v>025101510551010101010105551010952012810913271110101320510101010141510155105552015101010531031520201010105551010101051510105515305510551510101551051010105555155530</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-10.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1276,10 +1276,35 @@
       <c r="A101" t="str">
         <v>7</v>
       </c>
+      <c r="C101" t="str">
+        <v>695_百合虎皮_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F101" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" t="str">
+        <v>696_百合笑脸_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F102" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>8</v>
+      </c>
+      <c r="C103" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F103" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1334,7 +1359,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>025101510551010101010105551010952012810913271110101320510101010141510155105552015101010531031520201010105551010101051510105515305510551510101551051010105555155530</v>
+        <v>025101510551010101010105551010952012810913271110101320510101010141510155105552015101010531031520201010105551010101051510105515305510551510101551051010105555155532520</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-7-10.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-10.xlsx
@@ -1361,6 +1361,9 @@
       <c r="G2" t="str">
         <v>025101510551010101010105551010952012810913271110101320510101010141510155105552015101010531031520201010105551010101051510105515305510551510101551051010105555155532520</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
